--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -170,151 +170,151 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>MAYA</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
     <t>SILVERIO</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
     <t>GUILLERMO SAID</t>
   </si>
   <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
     <t>JESUS SAMUEL</t>
   </si>
   <si>
     <t>ROGELIO</t>
   </si>
   <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
     <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
   </si>
 </sst>
 </file>
@@ -803,7 +803,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -857,7 +857,7 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -1165,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1265,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1319,7 +1319,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -1704,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -2243,22 +2243,25 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>9</v>
+      </c>
       <c r="I2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2428,7 +2431,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2463,10 +2466,10 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -2483,10 +2486,10 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -2503,10 +2506,10 @@
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2517,16 +2520,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -2537,16 +2540,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -2557,22 +2560,22 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2580,33 +2583,33 @@
         <v>20330051920322</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920322</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -2617,36 +2620,36 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920323</v>
+        <v>20330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920380</v>
+        <v>20330051920325</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -2657,96 +2660,96 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920324</v>
+        <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B14" t="s">
         <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920397</v>
+        <v>20330051920396</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -2757,16 +2760,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B17" t="s">
         <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -2777,16 +2780,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B18" t="s">
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -2797,36 +2800,36 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B19" t="s">
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920396</v>
+        <v>20330051920330</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -2837,16 +2840,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920329</v>
+        <v>20330051920331</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -2857,16 +2860,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920329</v>
+        <v>20330051920331</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -2877,141 +2880,61 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920330</v>
+        <v>20330051920333</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920330</v>
+        <v>20330051920335</v>
       </c>
       <c r="B24" t="s">
         <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920331</v>
+        <v>20330051920335</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920331</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920333</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920335</v>
-      </c>
-      <c r="B28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920335</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3054,10 +2977,10 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -3068,13 +2991,13 @@
         <v>20330051920322</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -3085,13 +3008,13 @@
         <v>20330051920325</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3102,13 +3025,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3119,13 +3042,13 @@
         <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -3136,13 +3059,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3153,13 +3076,13 @@
         <v>20330051920330</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -3170,13 +3093,13 @@
         <v>20330051920331</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -3187,13 +3110,13 @@
         <v>20330051920335</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -3201,16 +3124,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3218,16 +3141,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B12" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3235,16 +3158,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920321</v>
+        <v>20330051920324</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -3252,16 +3175,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920323</v>
+        <v>20330051920396</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -3269,13 +3192,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920380</v>
+        <v>20330051920333</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>87</v>
@@ -3286,70 +3209,70 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920324</v>
+        <v>20330051920318</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920327</v>
+        <v>20330051920323</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920396</v>
+        <v>20330051920380</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920333</v>
+        <v>20330051920327</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3359,7 +3282,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3394,13 +3317,13 @@
         <v>20330051920321</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -3417,13 +3340,13 @@
         <v>20330051920321</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3440,13 +3363,13 @@
         <v>20330051920322</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -3463,13 +3386,13 @@
         <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3486,13 +3409,13 @@
         <v>20330051920325</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -3509,13 +3432,13 @@
         <v>20330051920325</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3532,13 +3455,13 @@
         <v>20330051920396</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -3555,13 +3478,13 @@
         <v>20330051920396</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -3578,13 +3501,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -3601,13 +3524,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -3624,13 +3547,13 @@
         <v>20330051920335</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -3647,13 +3570,13 @@
         <v>20330051920335</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -3667,16 +3590,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B14" t="s">
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -3690,16 +3613,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920320</v>
+        <v>20330051920324</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -3713,16 +3636,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920323</v>
+        <v>20330051920333</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -3731,98 +3654,6 @@
         <v>39</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920380</v>
-      </c>
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920324</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920327</v>
-      </c>
-      <c r="B19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920333</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -137,24 +137,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Castillo Cruz Carlos Samuel</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -170,46 +170,109 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>GAMEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
+    <t>MAYA</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>LARA</t>
@@ -218,34 +281,16 @@
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
+    <t>GUILLERMO SAID</t>
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
@@ -254,67 +299,22 @@
     <t>SURISADAY</t>
   </si>
   <si>
-    <t>MARCOS</t>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
   </si>
   <si>
     <t>ARIZBETH</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
+    <t>FRANCISCO YAEL</t>
   </si>
   <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
   </si>
 </sst>
 </file>
@@ -818,16 +818,16 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -854,13 +854,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -880,13 +880,13 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -895,16 +895,16 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -931,16 +931,16 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -957,7 +957,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -972,16 +972,16 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1011,13 +1011,13 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1034,7 +1034,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1049,16 +1049,16 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1085,16 +1085,16 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1126,16 +1126,16 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1168,7 +1168,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1203,16 +1203,16 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1239,10 +1239,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1280,16 +1280,16 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1342,7 +1342,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1357,16 +1357,16 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1393,16 +1393,16 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1419,7 +1419,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1434,16 +1434,16 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1470,16 +1470,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>-1</v>
@@ -1496,7 +1496,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1511,16 +1511,16 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1547,16 +1547,16 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>-1</v>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1588,16 +1588,16 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1624,16 +1624,16 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1665,16 +1665,16 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1727,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1742,16 +1742,16 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1778,16 +1778,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1804,7 +1804,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -1819,16 +1819,16 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -1855,16 +1855,16 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>-1</v>
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -1896,16 +1896,16 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -1932,16 +1932,16 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -1958,7 +1958,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -1973,16 +1973,16 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2009,16 +2009,16 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2035,7 +2035,7 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2050,16 +2050,16 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2089,10 +2089,10 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2112,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2127,16 +2127,16 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2163,16 +2163,16 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>-1</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
@@ -2243,30 +2243,30 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22.22</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>77.78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -2275,30 +2275,30 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>77.78</v>
+      </c>
+      <c r="G3">
+        <v>22.22</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>50</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>6.7</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -2307,19 +2307,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>42</v>
@@ -2339,19 +2339,19 @@
         <v>18</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -2371,30 +2371,30 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2431,7 +2431,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2466,33 +2466,33 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920322</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
@@ -2500,39 +2500,39 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920317</v>
+        <v>20330051920325</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920320</v>
+        <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
@@ -2540,19 +2540,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920321</v>
+        <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -2560,39 +2560,39 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920322</v>
+        <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920322</v>
+        <v>20330051920330</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
@@ -2600,19 +2600,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920324</v>
+        <v>20330051920331</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
@@ -2620,321 +2620,21 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920325</v>
+        <v>20330051920335</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920325</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920397</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920397</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920326</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920326</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920396</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920329</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920329</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920330</v>
-      </c>
-      <c r="B19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920330</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920331</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920331</v>
-      </c>
-      <c r="B22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920333</v>
-      </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920335</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920335</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2977,13 +2677,13 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2991,16 +2691,16 @@
         <v>20330051920322</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3008,16 +2708,16 @@
         <v>20330051920325</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3025,16 +2725,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3042,16 +2742,16 @@
         <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3059,16 +2759,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3076,16 +2776,16 @@
         <v>20330051920330</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3093,16 +2793,16 @@
         <v>20330051920331</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3110,112 +2810,112 @@
         <v>20330051920335</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920320</v>
+        <v>20330051920318</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920321</v>
+        <v>20330051920320</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920324</v>
+        <v>20330051920321</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920396</v>
+        <v>20330051920323</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920333</v>
+        <v>20330051920380</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920318</v>
+        <v>20330051920324</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -3226,13 +2926,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920323</v>
+        <v>20330051920327</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -3243,13 +2943,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920380</v>
+        <v>20330051920396</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -3260,13 +2960,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920327</v>
+        <v>20330051920333</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
         <v>98</v>
@@ -3282,7 +2982,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3314,19 +3014,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920321</v>
+        <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
@@ -3337,22 +3037,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920321</v>
+        <v>20330051920317</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3360,91 +3060,91 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920322</v>
+        <v>20330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920322</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -3452,48 +3152,48 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920396</v>
+        <v>20330051920326</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920396</v>
+        <v>20330051920326</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3501,22 +3201,22 @@
         <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3524,19 +3224,19 @@
         <v>20330051920329</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -3544,19 +3244,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920335</v>
+        <v>20330051920330</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -3567,42 +3267,42 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920335</v>
+        <v>20330051920330</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B14" t="s">
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
@@ -3613,19 +3313,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
@@ -3636,24 +3336,47 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920333</v>
+        <v>20330051920331</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920335</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -833,7 +833,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -910,7 +910,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -987,7 +987,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1023,7 +1023,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1064,7 +1064,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1100,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1141,7 +1141,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1218,7 +1218,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1295,7 +1295,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1372,7 +1372,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1449,7 +1449,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1526,7 +1526,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1562,7 +1562,7 @@
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1603,7 +1603,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1639,7 +1639,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1680,7 +1680,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1716,7 +1716,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1757,7 +1757,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1793,7 +1793,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1834,7 +1834,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1870,7 +1870,7 @@
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1911,7 +1911,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1988,7 +1988,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2024,7 +2024,7 @@
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2065,7 +2065,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2142,7 +2142,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2178,7 +2178,7 @@
         <v>-1</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2307,19 +2307,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="G4">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2982,7 +2982,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3060,16 +3060,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920321</v>
+        <v>20330051920397</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3083,39 +3083,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -3129,16 +3129,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3152,16 +3152,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -3175,16 +3175,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -3198,108 +3198,108 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920329</v>
+        <v>20330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920329</v>
+        <v>20330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920330</v>
+        <v>20330051920321</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920330</v>
+        <v>20330051920322</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920322</v>
+        <v>20330051920325</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -3313,16 +3313,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920325</v>
+        <v>20330051920331</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -3336,16 +3336,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920331</v>
+        <v>20330051920335</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -3354,29 +3354,6 @@
         <v>39</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920335</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -1020,7 +1020,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1061,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -1138,7 +1138,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1292,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1369,7 +1369,7 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1677,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -1754,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -2062,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -2098,7 +2098,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2243,19 +2243,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>9</v>
@@ -2982,7 +2982,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3244,22 +3244,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920321</v>
+        <v>20330051920320</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -3267,39 +3267,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920322</v>
+        <v>20330051920321</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920325</v>
+        <v>20330051920322</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -3313,16 +3313,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920331</v>
+        <v>20330051920325</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -3336,16 +3336,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920335</v>
+        <v>20330051920331</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -3354,6 +3354,29 @@
         <v>39</v>
       </c>
       <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920335</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -170,9 +170,24 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -182,6 +197,12 @@
     <t>LUNA</t>
   </si>
   <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -191,15 +212,33 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -218,15 +257,36 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
     <t>MARCOS</t>
   </si>
   <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
@@ -236,6 +296,12 @@
     <t>JESUS ANTONIO</t>
   </si>
   <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
     <t>JUAN GUILLERMO</t>
   </si>
   <si>
@@ -245,76 +311,10 @@
     <t>MICHELLE ROBERTA</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
     <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
   </si>
 </sst>
 </file>
@@ -889,7 +889,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -907,7 +907,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -943,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1197,7 +1197,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -1215,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1251,7 +1251,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1428,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1446,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1482,7 +1482,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1505,7 +1505,7 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -1523,7 +1523,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1559,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1582,7 +1582,7 @@
         <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1600,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -1636,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1813,7 +1813,7 @@
         <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -1831,7 +1831,7 @@
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -1890,7 +1890,7 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -1908,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -1944,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1967,7 +1967,7 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>7</v>
@@ -1985,7 +1985,7 @@
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2021,7 +2021,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2121,7 +2121,7 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>6</v>
@@ -2139,7 +2139,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2175,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2243,25 +2243,25 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>44.44</v>
+        <v>72.22</v>
       </c>
       <c r="G2">
-        <v>5.56</v>
+        <v>27.78</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2431,7 +2431,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2456,186 +2456,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920317</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920322</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920325</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920397</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920329</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920330</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920331</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920335</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2677,160 +2497,160 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920322</v>
+        <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920325</v>
+        <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920397</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920326</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920329</v>
+        <v>20330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920330</v>
+        <v>20330051920380</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920331</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
         <v>56</v>
       </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920335</v>
+        <v>20330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920318</v>
+        <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -2841,13 +2661,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920320</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
@@ -2858,13 +2678,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920321</v>
+        <v>20330051920327</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
         <v>92</v>
@@ -2875,13 +2695,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920323</v>
+        <v>20330051920396</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -2892,13 +2712,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920380</v>
+        <v>20330051920329</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2909,13 +2729,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920324</v>
+        <v>20330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -2926,13 +2746,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920327</v>
+        <v>20330051920331</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -2943,13 +2763,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920396</v>
+        <v>20330051920333</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -2960,13 +2780,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
         <v>98</v>
@@ -2982,7 +2802,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3020,10 +2840,10 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3032,7 +2852,7 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3043,10 +2863,10 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3063,13 +2883,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3086,13 +2906,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3101,7 +2921,7 @@
         <v>39</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3109,13 +2929,13 @@
         <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -3132,13 +2952,13 @@
         <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3147,7 +2967,7 @@
         <v>39</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3155,13 +2975,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -3178,13 +2998,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -3193,21 +3013,21 @@
         <v>39</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920330</v>
+        <v>20330051920320</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -3216,27 +3036,27 @@
         <v>39</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920330</v>
+        <v>20330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3244,140 +3064,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920320</v>
+        <v>20330051920330</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>77</v>
       </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12">
         <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920321</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920322</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920325</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920331</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920335</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -845,10 +845,10 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -922,10 +922,10 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -999,10 +999,10 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1076,10 +1076,10 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1153,10 +1153,10 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1230,10 +1230,10 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1248,10 +1248,10 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1307,10 +1307,10 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1328,7 +1328,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1384,10 +1384,10 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1402,7 +1402,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1461,10 +1461,10 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1538,10 +1538,10 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1615,10 +1615,10 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1692,10 +1692,10 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1713,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1769,10 +1769,10 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1846,10 +1846,10 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1864,7 +1864,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -1923,10 +1923,10 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2000,10 +2000,10 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2018,10 +2018,10 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2077,10 +2077,10 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2098,7 +2098,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2154,10 +2154,10 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2175,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2243,19 +2243,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>72.22</v>
+        <v>55.56</v>
       </c>
       <c r="G2">
-        <v>27.78</v>
+        <v>44.44</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2802,7 +2802,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3064,24 +3064,93 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
+        <v>20330051920322</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
         <v>20330051920330</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>62</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>77</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>95</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
         <v>41</v>
       </c>
-      <c r="G12">
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920331</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920335</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -836,10 +836,10 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -857,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -913,10 +913,10 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -990,10 +990,10 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1067,10 +1067,10 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1088,7 +1088,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1144,10 +1144,10 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1221,10 +1221,10 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1298,10 +1298,10 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1375,10 +1375,10 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1452,10 +1452,10 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1470,10 +1470,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1529,10 +1529,10 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1547,10 +1547,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1606,10 +1606,10 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1683,10 +1683,10 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1760,10 +1760,10 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1837,10 +1837,10 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1855,7 +1855,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -1914,10 +1914,10 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1991,10 +1991,10 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2068,10 +2068,10 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2145,10 +2145,10 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2166,7 +2166,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -140,10 +140,10 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -842,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -919,7 +919,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -937,7 +937,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -996,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1014,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1073,7 +1073,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1150,7 +1150,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -1245,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1304,7 +1304,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1381,7 +1381,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1458,7 +1458,7 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1476,7 +1476,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1535,7 +1535,7 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1553,7 +1553,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1612,7 +1612,7 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1630,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1766,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -1843,7 +1843,7 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -1861,7 +1861,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1920,7 +1920,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2074,7 +2074,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2092,7 +2092,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2151,7 +2151,7 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2169,7 +2169,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -2275,19 +2275,19 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="G3">
-        <v>22.22</v>
+        <v>11.11</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -2307,19 +2307,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="G4">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2802,7 +2802,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2872,7 +2872,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2880,22 +2880,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920397</v>
+        <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2903,22 +2903,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920397</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -2926,22 +2926,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920326</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -2949,16 +2949,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920326</v>
+        <v>20330051920397</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -2972,22 +2972,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920329</v>
+        <v>20330051920326</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3018,22 +3018,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920320</v>
+        <v>20330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3041,22 +3041,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920321</v>
+        <v>20330051920331</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3064,16 +3064,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920322</v>
+        <v>20330051920335</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -3082,75 +3082,6 @@
         <v>39</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920330</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920331</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920335</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20221.xlsx
+++ b/grupos/5ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -140,10 +140,10 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -851,7 +851,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -928,7 +928,7 @@
         <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -946,7 +946,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1005,7 +1005,7 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1082,7 +1082,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1100,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1159,7 +1159,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1177,7 +1177,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1236,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1254,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1313,7 +1313,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1390,7 +1390,7 @@
         <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1408,7 +1408,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1467,7 +1467,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1485,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1544,7 +1544,7 @@
         <v>4</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1562,7 +1562,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1621,7 +1621,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1698,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1775,7 +1775,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1852,7 +1852,7 @@
         <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -1947,7 +1947,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2006,7 +2006,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2083,7 +2083,7 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2160,7 +2160,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -2275,19 +2275,19 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="G3">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -2307,19 +2307,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2802,7 +2802,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2857,22 +2857,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2880,22 +2880,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2903,22 +2903,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -2926,16 +2926,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920322</v>
+        <v>20330051920397</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -2949,16 +2949,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -2972,16 +2972,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -2995,16 +2995,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920329</v>
+        <v>20330051920331</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -3018,70 +3018,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920330</v>
+        <v>20330051920335</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920331</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920335</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
